--- a/data/credit_bond_2026-09-23.xlsx
+++ b/data/credit_bond_2026-09-23.xlsx
@@ -951,7 +951,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1400/2.1000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-23.xlsx
+++ b/data/credit_bond_2026-09-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-23</t>
+          <t>数据来源：DM    2026-09-24</t>
         </is>
       </c>
     </row>
@@ -692,60 +692,72 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26三峡银行债01</t>
+          <t>26桂债04</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>09-23 17:00</t>
-        </is>
-      </c>
-      <c r="C3" s="3"/>
+          <t>09-23 19:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>520498.SZ</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>69.06</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25三峡银行科创债01(柜台)</t>
+          <t>26桂债03</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.00Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>1.7065</t>
+          <t>2.1280</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1200/2.1000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>广西金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>A- 66.52</t>
+          <t>B- 44.64</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -755,7 +767,7 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:30</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -765,19 +777,19 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -786,17 +798,25 @@
         </is>
       </c>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>广西壮族自治区</t>
+        </is>
+      </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC3" s="3"/>
+          <t>本期债券募集资金拟全部用于偿还有息债务</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>中国银河证券股份有限公司,华创证券有限责任公司,国海证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -806,22 +826,22 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年金融债券(第一期)</t>
+          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
@@ -832,12 +852,12 @@
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
@@ -847,27 +867,27 @@
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -900,17 +920,17 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26桂债04</t>
+          <t>26重庆三峡银行债01</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-23 18:00</t>
+          <t>09-23 17:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>520498.SZ</t>
+          <t>212680061.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -919,49 +939,51 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>37.06</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26桂债03</t>
+          <t>25三峡银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.00Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>2.1275</t>
+          <t>1.7065</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>2.1400/2.1000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 40.89</t>
+          <t>A- 66.60</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -971,7 +993,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 09:30</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -981,19 +1003,19 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1002,25 +1024,17 @@
         </is>
       </c>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>广西壮族自治区</t>
-        </is>
-      </c>
+      <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还有息债务</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>中国银河证券股份有限公司,华创证券有限责任公司,国海证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1030,22 +1044,22 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>重庆三峡银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2029-09-24</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1056,12 +1070,12 @@
       </c>
       <c r="AM4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
@@ -1071,27 +1085,27 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-23.xlsx
+++ b/data/credit_bond_2026-09-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 44.64</t>
+          <t>B- 47.67</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A- 66.60</t>
+          <t>A- 65.87</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1065,7 +1065,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">

--- a/data/credit_bond_2026-09-23.xlsx
+++ b/data/credit_bond_2026-09-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_2026-09-23.xlsx
+++ b/data/credit_bond_2026-09-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-28" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-29" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-28</t>
+          <t>数据来源：DM    2026-09-29</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26桂债04</t>
+          <t>26重庆三峡银行债01</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>09-23 19:00</t>
+          <t>09-23 17:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>520498.SZ</t>
+          <t>212680061.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -711,53 +711,51 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>1.90 ~ 2.50</t>
-        </is>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="H3" s="4" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>69.06</v>
+        <v>37.06</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26桂债03</t>
+          <t>25三峡银行科创债01(柜台)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.00Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.1280</t>
+          <t>1.7065</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>2.1200/2.1000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司</t>
+          <t>重庆三峡银行股份有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>B- 47.67</t>
+          <t>A- 66.24</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -767,7 +765,7 @@
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>09-23 15:00</t>
+          <t>09-23 09:30</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
@@ -777,19 +775,19 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
@@ -798,25 +796,17 @@
         </is>
       </c>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="inlineStr">
-        <is>
-          <t>广西壮族自治区</t>
-        </is>
-      </c>
+      <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于偿还有息债务</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>中国银河证券股份有限公司,华创证券有限责任公司,国海证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF3" s="3" t="inlineStr">
@@ -826,38 +816,38 @@
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
+          <t>重庆三峡银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2029-09-24</t>
         </is>
       </c>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AO3" s="3" t="inlineStr">
@@ -867,27 +857,27 @@
       </c>
       <c r="AP3" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ3" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>金融控股</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT3" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU3" s="3" t="inlineStr">
@@ -920,17 +910,17 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26重庆三峡银行债01</t>
+          <t>26桂债04</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-23 17:00</t>
+          <t>09-23 19:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>212680061.IB</t>
+          <t>520498.SZ</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -939,51 +929,55 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.50</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>37.06</v>
+        <v>69.06</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25三峡银行科创债01(柜台)</t>
+          <t>26桂债03</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>4.00Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.7065</t>
+          <t>2.1280</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1200/2.1000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司</t>
+          <t>广西金融投资集团有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>A- 65.87</t>
+          <t>B- 44.11</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -993,7 +987,7 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>09-23 09:30</t>
+          <t>09-23 15:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
@@ -1003,19 +997,21 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>3.76</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1024,17 +1020,25 @@
         </is>
       </c>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>广西壮族自治区</t>
+        </is>
+      </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC4" s="3"/>
+          <t>本期债券募集资金拟全部用于偿还有息债务</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>中国银河证券股份有限公司,华创证券有限责任公司,国海证券股份有限公司,中信建投证券股份有限公司,广发证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1044,40 +1048,40 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>重庆三峡银行股份有限公司2026年金融债券(第一期)</t>
+          <t>广西金融投资集团有限公司2026年面向专业投资者非公开发行公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-24</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>金融</t>
@@ -1085,27 +1089,27 @@
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>金融控股</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
